--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-cim11-mms</t>
+    <t>OID:2.16.840.1.113883.6.347</t>
   </si>
   <si>
     <t>Version</t>
@@ -49,7 +49,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Classification Internationale des Maladies 11ème révision pour les statistiques de mortalité et de morbidité</t>
+    <t>Classification internationale des maladies (11eme révision). Linéarisation pour les statistiques de morbi-mortalité</t>
   </si>
   <si>
     <t>Status</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T10:40:39+00:00</t>
+    <t>2024-11-19T13:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T13:31:18+00:00</t>
+    <t>2024-11-19T18:17:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T18:17:10+00:00</t>
+    <t>2024-11-20T08:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T08:37:30+00:00</t>
+    <t>2024-11-20T15:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T15:15:20+00:00</t>
+    <t>2024-11-22T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T15:33:20+00:00</t>
+    <t>2024-11-26T16:33:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T16:33:37+00:00</t>
+    <t>2024-11-28T11:58:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T11:58:57+00:00</t>
+    <t>2024-12-05T16:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T16:56:49+00:00</t>
+    <t>2024-12-10T08:10:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:10:26+00:00</t>
+    <t>2024-12-11T08:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:03:58+00:00</t>
+    <t>2024-12-11T13:32:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T13:32:58+00:00</t>
+    <t>2024-12-11T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:07:35+00:00</t>
+    <t>2024-12-11T17:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T17:05:38+00:00</t>
+    <t>2024-12-12T10:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T10:04:28+00:00</t>
+    <t>2024-12-12T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
